--- a/output/第10期計画_社内作業ファイルの点検.xlsx
+++ b/output/第10期計画_社内作業ファイルの点検.xlsx
@@ -4023,19 +4023,19 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>26500</v>
+        <v>26451</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>9081</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.3426638307472759</v>
+        <v>0.3432960876997369</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>5629</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>-0.03628903913764414</v>
+        <v>-0.03806392960974592</v>
       </c>
       <c r="H7" s="24" t="n">
         <v>-0.01039298106666942</v>
@@ -4051,19 +4051,19 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>25422</v>
+        <v>25340</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>8982</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.3533165247571103</v>
+        <v>0.3544701575135306</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>5366</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.07547929823307176</v>
+        <v>-0.07848817597056146</v>
       </c>
       <c r="H8" s="24" t="n">
         <v>-0.02112261965885909</v>
@@ -4079,19 +4079,19 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>24358</v>
+        <v>24255</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>9095</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.3733749117096015</v>
+        <v>0.3749627127940499</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>5184</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.1141827466980465</v>
+        <v>-0.1179337905950126</v>
       </c>
       <c r="H9" s="24" t="n">
         <v>-0.008855510948111989</v>
@@ -4107,19 +4107,19 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>23341</v>
+        <v>23168</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>8933</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.3827178367597626</v>
+        <v>0.3855733864372572</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>5069</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.1511776877044497</v>
+        <v>-0.157464050729975</v>
       </c>
       <c r="H10" s="24" t="n">
         <v>-0.02648377747505037</v>
@@ -4199,7 +4199,7 @@
         <v>0.06498189554995104</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.08030265171237794</v>
+        <v>0.0812245884926226</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -4227,7 +4227,7 @@
         <v>0.07602887433457073</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.2418141636446379</v>
+        <v>-0.2519370852179702</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>-0.1784823109572198</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.2755540623787469</v>
+        <v>-0.2846420234836068</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
